--- a/documentation/C supported tokens.xlsx
+++ b/documentation/C supported tokens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iacopo\Desktop\python\HBM-s-NTM-autocal-compiler-MS-ES1-\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F643EE0-7898-425C-8782-13067C2EFC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7401A64-1E04-40B8-81D8-D73F34E503BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>N°</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Colonna9</t>
-  </si>
-  <si>
     <t>Colonna10</t>
   </si>
   <si>
@@ -57,15 +54,12 @@
     <t>No</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>Supported</t>
   </si>
   <si>
-    <t>Substitute the actual ROR read untill a better way is made</t>
-  </si>
-  <si>
-    <t>Substitute the actual ROR writes untill a better way is made</t>
-  </si>
-  <si>
     <t>Sets the clockspeed</t>
   </si>
   <si>
@@ -93,9 +87,6 @@
     <t>functions</t>
   </si>
   <si>
-    <t>For now only "main" is supported</t>
-  </si>
-  <si>
     <t>int variable</t>
   </si>
   <si>
@@ -114,6 +105,9 @@
     <t>variable name</t>
   </si>
   <si>
+    <t>&lt;init value&gt;</t>
+  </si>
+  <si>
     <t>implicitly initialize them to 0, max 4 variables in row.</t>
   </si>
   <si>
@@ -141,9 +135,6 @@
     <t>channel</t>
   </si>
   <si>
-    <t>signal</t>
-  </si>
-  <si>
     <t>expression</t>
   </si>
   <si>
@@ -168,13 +159,80 @@
     <t>expression term N</t>
   </si>
   <si>
-    <t>&lt;init value&gt; or expression term 1</t>
-  </si>
-  <si>
-    <t>none or expression term 2</t>
-  </si>
-  <si>
-    <t>none or expression term N</t>
+    <t>For now only "main" is technicaly supported, but not callable</t>
+  </si>
+  <si>
+    <t>MSES direct output</t>
+  </si>
+  <si>
+    <t>clockspeed &lt;clockspeed&gt;</t>
+  </si>
+  <si>
+    <t>int variable = 2 * var2</t>
+  </si>
+  <si>
+    <t>varinitexpression</t>
+  </si>
+  <si>
+    <t>buffer &lt;init value&gt;
+save &lt;variable name&gt;</t>
+  </si>
+  <si>
+    <t>value or var</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Substitutes the actual ROR read untill a better way is made, does not currently support changing channels at runtime</t>
+  </si>
+  <si>
+    <t>eval &lt;expression&gt;
+save &lt;variable name&gt;</t>
+  </si>
+  <si>
+    <t>Substitutes the actual ROR writes untill a better way is made, does not currently support changing channels at runtime and needs to read from a variable</t>
+  </si>
+  <si>
+    <t>listen &lt;channel&gt;
+save &lt;variable&gt;</t>
+  </si>
+  <si>
+    <t>load &lt;variable&gt;
+round
+send &lt;channel&gt;</t>
+  </si>
+  <si>
+    <t>while(true)</t>
+  </si>
+  <si>
+    <t>infloop</t>
+  </si>
+  <si>
+    <t>dest &lt;infloop N&gt;
+   ….
+Jmp &lt;infloop N&gt;</t>
+  </si>
+  <si>
+    <t>writing timings</t>
+  </si>
+  <si>
+    <t>Writing two values on the same channel makes a mess, the compiler should warn about it or fix it</t>
+  </si>
+  <si>
+    <t>if(condition)</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>For now only supports one condition and no logical operators</t>
   </si>
 </sst>
 </file>
@@ -241,7 +299,84 @@
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -292,97 +427,6 @@
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -606,24 +650,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{93B6D195-4A67-4502-B231-219B1C36F3C5}" name="Tabella1" displayName="Tabella1" ref="A1:O33" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{93B6D195-4A67-4502-B231-219B1C36F3C5}" name="Tabella1" displayName="Tabella1" ref="A1:O33" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:O33" xr:uid="{93B6D195-4A67-4502-B231-219B1C36F3C5}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{B52BBF53-AE45-4136-BA41-E7A07D03D2CB}" name="N°" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{CE21D4EE-4DEB-4021-A54F-C0444EC152B3}" name="Instruction" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{C90AC815-0C0D-48FE-A64A-6BC4E22A1168}" name="Supported" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{B37FE39F-0090-4200-991B-AEABDD1E5B16}" name="Notes" dataDxfId="0"/>
-    <tableColumn id="15" xr3:uid="{B4F967DC-6EE0-427E-9DE4-F412A60D18F0}" name="Token type" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{715D9404-1C3D-426B-9F47-FDEB95471762}" name="Token D1" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{9EBDF304-C56E-4097-9387-1C04785F56C2}" name="Token D2" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{33FB0CEA-A8A5-4692-BE4E-BB2EBED97F61}" name="Token D3" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{E21AF26C-EBE4-4BFD-BB1E-F81152CBE537}" name="Token D4" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{46E57B1F-B596-4725-B713-993E6FE642FB}" name="Colonna9" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{8E7B476C-78E7-4155-8662-E1E210FB1C4A}" name="Colonna10" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{FCD7FFEC-0280-45A6-B7ED-AC0717F0CAC6}" name="Colonna11" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{91E1C77A-8C54-43B2-A697-5CB2C2519117}" name="Colonna12" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{22802FE0-9E01-4E2E-812A-9EFD959288FF}" name="Colonna13" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{66692320-770B-47E0-A4EF-918AFB63D888}" name="Colonna14" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{B52BBF53-AE45-4136-BA41-E7A07D03D2CB}" name="N°" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{CE21D4EE-4DEB-4021-A54F-C0444EC152B3}" name="Instruction" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{C90AC815-0C0D-48FE-A64A-6BC4E22A1168}" name="Supported" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{B37FE39F-0090-4200-991B-AEABDD1E5B16}" name="Notes" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{B4F967DC-6EE0-427E-9DE4-F412A60D18F0}" name="Token type" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{715D9404-1C3D-426B-9F47-FDEB95471762}" name="Token D1" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{9EBDF304-C56E-4097-9387-1C04785F56C2}" name="Token D2" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{33FB0CEA-A8A5-4692-BE4E-BB2EBED97F61}" name="Token D3" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{E21AF26C-EBE4-4BFD-BB1E-F81152CBE537}" name="Token D4" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{46E57B1F-B596-4725-B713-993E6FE642FB}" name="MSES direct output" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{8E7B476C-78E7-4155-8662-E1E210FB1C4A}" name="Colonna10" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{FCD7FFEC-0280-45A6-B7ED-AC0717F0CAC6}" name="Colonna11" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{91E1C77A-8C54-43B2-A697-5CB2C2519117}" name="Colonna12" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{22802FE0-9E01-4E2E-812A-9EFD959288FF}" name="Colonna13" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{66692320-770B-47E0-A4EF-918AFB63D888}" name="Colonna14" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -899,11 +943,12 @@
     <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.85546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="14" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -920,95 +965,99 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:15" ht="63" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="J2" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
     </row>
-    <row r="3" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="J3" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -1020,24 +1069,26 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
+      <c r="J4" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -1049,10 +1100,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="5"/>
@@ -1067,24 +1118,24 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="5"/>
@@ -1101,13 +1152,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -1126,13 +1177,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -1151,28 +1202,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -1184,26 +1233,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1212,51 +1261,81 @@
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="4"/>
+      <c r="B11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="4"/>
+      <c r="B12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="G12" s="4"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="J12" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
     </row>
-    <row r="13" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="B13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="4"/>
@@ -1269,15 +1348,25 @@
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="B14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="G14" s="4"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -1651,14 +1740,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="Planned">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="Planned">
       <formula>NOT(ISERROR(SEARCH("Planned",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",C1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Partial">
+      <formula>NOT(ISERROR(SEARCH("Partial",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
